--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>런던필라테스 &amp; 피트니스 &amp; PT 오리역점</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>londonpilates@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1358-9680</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 구미로9번길 17 광림빌딩 6층</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londonpilates</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,32 +606,28 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wtxy8ap</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>815</v>
+        <v>561</v>
       </c>
       <c r="Q2" t="n">
-        <v>559</v>
+        <v>1070</v>
       </c>
       <c r="R2" t="n">
-        <v>1374</v>
+        <v>1631</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +636,55 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1973226342</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973226342</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>주피티</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jooptofficial@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1320-3338</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 수정구 위례동로 153 에이플타워 903호 주피티</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/joopt_</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>67</v>
+        <v>1766</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>249</v>
       </c>
       <c r="R3" t="n">
-        <v>78</v>
+        <v>2015</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1251628109</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251628109</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,39 +756,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>크레이지핏 PT</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>krazyfit@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1488-5883</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>O</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -804,22 +804,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P4" t="n">
-        <v>526</v>
+        <v>2535</v>
       </c>
       <c r="Q4" t="n">
-        <v>1638</v>
+        <v>322</v>
       </c>
       <c r="R4" t="n">
-        <v>2164</v>
+        <v>2857</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1628554288</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628554288</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -850,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>베러댄 휘트니스 분당야탑점</t>
+          <t>와이투짐 야탑역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56zqrwcwsv@naver.com</t>
+          <t>y2gym2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1438-9698</t>
+          <t>0507-1352-8844</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/56zqrwcwsv</t>
+          <t>https://blog.naver.com/y2gym2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -898,7 +898,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="Q5" t="n">
-        <v>2033</v>
+        <v>1559</v>
       </c>
       <c r="R5" t="n">
-        <v>2415</v>
+        <v>1939</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,51 +922,35 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1013682807</t>
+          <t>1930702763</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013682807</t>
+          <t>https://m.place.naver.com/place/1930702763</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>와이투짐 야탑역점</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>y2gym2@naver.com</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1352-8844</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/y2gym2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,12 +960,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -992,22 +976,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1517</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1893</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,51 +1000,35 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1930702763</t>
+          <t>7174180</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930702763</t>
+          <t>https://m.place.naver.com/place/7174180</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>쿼드짐</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>quadgym@naver.com</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1303-9415</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/quadgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,12 +1038,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,17 +1059,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1078,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>7312861</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/7312861</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1188,17 +1156,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7174180</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7174180</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1244,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1322,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1422,173 +1390,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7312861</t>
+          <t>7536599</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7312861</t>
+          <t>https://m.place.naver.com/place/7536599</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7173992</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7173992</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7536599</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7536599</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -423,10 +423,10 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -624,10 +624,10 @@
         <v>561</v>
       </c>
       <c r="Q2" t="n">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="R2" t="n">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,45 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>humblefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -710,22 +706,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>1766</v>
+        <v>141</v>
       </c>
       <c r="Q3" t="n">
-        <v>249</v>
+        <v>1437</v>
       </c>
       <c r="R3" t="n">
-        <v>2015</v>
+        <v>1578</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2535</v>
+        <v>2540</v>
       </c>
       <c r="Q4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R4" t="n">
-        <v>2857</v>
+        <v>2863</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -850,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>와이투짐 야탑역점</t>
+          <t>쓰리핏PT 분당정자점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>y2gym2@naver.com</t>
+          <t>3fits@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1352-8844</t>
+          <t>0507-1409-3559</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/y2gym2</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -898,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P5" t="n">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="Q5" t="n">
-        <v>1559</v>
+        <v>800</v>
       </c>
       <c r="R5" t="n">
-        <v>1939</v>
+        <v>1157</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1930702763</t>
+          <t>1845673431</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930702763</t>
+          <t>https://m.place.naver.com/place/1845673431</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1006,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1084,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1162,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1240,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1318,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1396,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n5lk</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -624,10 +628,10 @@
         <v>561</v>
       </c>
       <c r="Q2" t="n">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="R2" t="n">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnvkt3b</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>경기 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +885,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,18 +895,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vrph</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,44 +559,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>카빈 PT 필라테스 성남모란점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>leejsjjd@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>0507-1364-7427</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 중원구 광명로 8 301호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://booking.naver.com/booking/6/bizes/1011819</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n5lk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>561</v>
+        <v>70</v>
       </c>
       <c r="Q2" t="n">
-        <v>1074</v>
+        <v>316</v>
       </c>
       <c r="R2" t="n">
-        <v>1635</v>
+        <v>386</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>1305151021</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/1305151021</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wnvkt3b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>141</v>
+        <v>561</v>
       </c>
       <c r="Q3" t="n">
-        <v>1437</v>
+        <v>1074</v>
       </c>
       <c r="R3" t="n">
-        <v>1578</v>
+        <v>1635</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +747,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,17 +798,13 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2540</v>
+        <v>1765</v>
       </c>
       <c r="Q4" t="n">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="R4" t="n">
-        <v>2863</v>
+        <v>2015</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,34 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>쓰리핏PT 분당정자점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1409-3559</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -900,17 +892,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vrph</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>357</v>
+        <v>2540</v>
       </c>
       <c r="Q5" t="n">
-        <v>800</v>
+        <v>323</v>
       </c>
       <c r="R5" t="n">
-        <v>1157</v>
+        <v>2863</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1845673431</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845673431</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -949,25 +937,41 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>크레이지핏 PT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>krazyfit@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1488-5883</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,22 +992,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>535</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1437</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1972</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7174180</t>
+          <t>1628554288</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7174180</t>
+          <t>https://m.place.naver.com/place/1628554288</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1027,35 +1031,51 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>쓰리핏PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1409-3559</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1066,22 +1086,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1090,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7312861</t>
+          <t>1845673431</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7312861</t>
+          <t>https://m.place.naver.com/place/1845673431</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1168,12 +1188,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>7174180</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/7174180</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,12 +1266,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>7312861</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/7312861</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,12 +1344,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,15 +1422,171 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>2600001</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2600001</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>7167332</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7167332</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>7536599</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7536599</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -559,44 +559,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>카빈 PT 필라테스 성남모란점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>leejsjjd@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1364-7427</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 중원구 광명로 8 301호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1011819</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="Q2" t="n">
-        <v>316</v>
+        <v>1437</v>
       </c>
       <c r="R2" t="n">
-        <v>386</v>
+        <v>1578</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1305151021</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1305151021</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>561</v>
+        <v>1340</v>
       </c>
       <c r="Q3" t="n">
-        <v>1074</v>
+        <v>473</v>
       </c>
       <c r="R3" t="n">
-        <v>1635</v>
+        <v>1813</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,38 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -804,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1765</v>
+        <v>2540</v>
       </c>
       <c r="Q4" t="n">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="R4" t="n">
-        <v>2015</v>
+        <v>2863</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,39 +846,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>크레이지핏 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>krazyfit@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1488-5883</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -898,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2540</v>
+        <v>535</v>
       </c>
       <c r="Q5" t="n">
-        <v>323</v>
+        <v>1437</v>
       </c>
       <c r="R5" t="n">
-        <v>2863</v>
+        <v>1972</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1628554288</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1628554288</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>크레이지핏 PT</t>
+          <t>쓰리핏PT 분당정자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>krazyfit@naver.com</t>
+          <t>3fits@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1488-5883</t>
+          <t>0507-1409-3559</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1001,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>535</v>
+        <v>357</v>
       </c>
       <c r="Q6" t="n">
-        <v>1437</v>
+        <v>800</v>
       </c>
       <c r="R6" t="n">
-        <v>1972</v>
+        <v>1157</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1628554288</t>
+          <t>1845673431</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628554288</t>
+          <t>https://m.place.naver.com/place/1845673431</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1031,51 +1027,35 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>쓰리핏PT 분당정자점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3fits@naver.com</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1409-3559</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1086,22 +1066,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1157</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1090,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1845673431</t>
+          <t>7174180</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845673431</t>
+          <t>https://m.place.naver.com/place/7174180</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1188,12 +1168,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7174180</t>
+          <t>7312861</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7174180</t>
+          <t>https://m.place.naver.com/place/7312861</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1266,12 +1246,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7312861</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7312861</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,12 +1324,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1422,12 +1402,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,93 +1480,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>7536599</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/7536599</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7536599</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7536599</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>141</v>
+        <v>561</v>
       </c>
       <c r="Q2" t="n">
-        <v>1437</v>
+        <v>1075</v>
       </c>
       <c r="R2" t="n">
-        <v>1578</v>
+        <v>1636</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -928,56 +928,40 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>쓰리핏PT 분당정자점</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3fits@naver.com</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1409-3559</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,22 +972,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1157</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +996,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1845673431</t>
+          <t>7174180</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845673431</t>
+          <t>https://m.place.naver.com/place/7174180</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1090,17 +1074,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7174180</t>
+          <t>7312861</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7174180</t>
+          <t>https://m.place.naver.com/place/7312861</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1152,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7312861</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7312861</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1246,17 +1230,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1308,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1402,95 +1386,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>7540516</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/7540516</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7536599</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7536599</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>561</v>
+        <v>141</v>
       </c>
       <c r="Q2" t="n">
-        <v>1075</v>
+        <v>1437</v>
       </c>
       <c r="R2" t="n">
-        <v>1636</v>
+        <v>1578</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -933,35 +933,51 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>쓰리핏PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1409-3559</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://3fitpt.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -972,22 +988,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1156</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -996,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7174180</t>
+          <t>1845673431</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7174180</t>
+          <t>https://m.place.naver.com/place/1845673431</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1074,12 +1090,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7312861</t>
+          <t>7174180</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7312861</t>
+          <t>https://m.place.naver.com/place/7174180</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,12 +1168,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7544685</t>
+          <t>7312861</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7544685</t>
+          <t>https://m.place.naver.com/place/7312861</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,12 +1246,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>7544685</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/7544685</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,12 +1324,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1386,15 +1402,93 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>7167332</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7167332</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>7540516</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7540516</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -421,9 +421,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -559,34 +559,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +616,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>141</v>
+        <v>1765</v>
       </c>
       <c r="Q2" t="n">
-        <v>1437</v>
+        <v>250</v>
       </c>
       <c r="R2" t="n">
-        <v>1578</v>
+        <v>2015</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,39 +657,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +714,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1340</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1813</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="Q4" t="n">
         <v>323</v>
       </c>
       <c r="R4" t="n">
-        <v>2863</v>
+        <v>2865</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="Q5" t="n">
         <v>1437</v>
       </c>
       <c r="R5" t="n">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -967,7 +975,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +985,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +996,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -421,9 +421,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,38 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>런던필라테스 &amp; 피트니스 &amp; PT 오리역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>londonpilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1358-9680</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기 성남시 분당구 구미로9번길 17 광림빌딩 6층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/londonpilates</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,13 +606,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wtxy8ap</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1765</v>
+        <v>814</v>
       </c>
       <c r="Q2" t="n">
-        <v>250</v>
+        <v>562</v>
       </c>
       <c r="R2" t="n">
-        <v>2015</v>
+        <v>1376</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1973226342</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1973226342</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,38 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>쿼드짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>quadgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1303-9415</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/quadgym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -714,7 +710,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1759307500</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1759307500</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="Q4" t="n">
         <v>323</v>
       </c>
       <c r="R4" t="n">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -914,10 +910,10 @@
         <v>538</v>
       </c>
       <c r="Q5" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="R5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -975,7 +971,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -985,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -996,7 +992,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1005,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q6" t="n">
         <v>800</v>
       </c>
       <c r="R6" t="n">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1030,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1104,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1182,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1260,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1338,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1416,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1484,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7540516</t>
+          <t>7536599</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7540516</t>
+          <t>https://m.place.naver.com/place/7536599</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/성남_PT.xlsx
+++ b/naver-place-crawler/results_health/성남_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,39 +559,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>런던필라테스 &amp; 피트니스 &amp; PT 오리역점</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>londonpilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1358-9680</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 구미로9번길 17 광림빌딩 6층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londonpilates</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -606,17 +610,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wtxy8ap</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1376</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1973226342</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973226342</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/quadgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pnpp</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>82</v>
+        <v>1341</v>
       </c>
       <c r="Q3" t="n">
-        <v>102</v>
+        <v>473</v>
       </c>
       <c r="R3" t="n">
-        <v>184</v>
+        <v>1814</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -778,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,20 +792,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -872,12 +880,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,18 +895,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44lbo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Q5" t="n">
         <v>1438</v>
       </c>
       <c r="R5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -949,7 +961,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>3fitpt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vrph</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
